--- a/Test Results/Excel/Selenium_Automation_Report.xlsx
+++ b/Test Results/Excel/Selenium_Automation_Report.xlsx
@@ -101,7 +101,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>3.17s</t>
+    <t>3.18s</t>
   </si>
   <si>
     <t>N/A</t>
@@ -136,7 +136,7 @@
     <t>Validation markers light up on blank text-inputs.</t>
   </si>
   <si>
-    <t>6.47s</t>
+    <t>6.48s</t>
   </si>
   <si>
     <t>TC_WEB_AUTH_003</t>
@@ -148,7 +148,7 @@
     <t>Verify that a student can successfully log in on web layout. (Variation 3)</t>
   </si>
   <si>
-    <t>9.50s</t>
+    <t>9.49s</t>
   </si>
   <si>
     <t>TC_WEB_AUTH_004</t>
@@ -1279,7 +1279,7 @@
     <t>Input fields contain typed strings.</t>
   </si>
   <si>
-    <t>12.57s</t>
+    <t>12.50s</t>
   </si>
   <si>
     <t>TC_WEB_FORM_002</t>
@@ -1681,7 +1681,7 @@
     <t>Status shifts back to Register button.</t>
   </si>
   <si>
-    <t>13.50s</t>
+    <t>13.59s</t>
   </si>
   <si>
     <t>TC_WEB_CRUD_003</t>
@@ -1693,7 +1693,7 @@
     <t>Verify registering updates status on database. (Variation 3)</t>
   </si>
   <si>
-    <t>13.51s</t>
+    <t>13.56s</t>
   </si>
   <si>
     <t>TC_WEB_CRUD_004</t>
@@ -2705,7 +2705,7 @@
     <t>Dashboard continues loading direct, bypassing login screen.</t>
   </si>
   <si>
-    <t>14.59s</t>
+    <t>14.56s</t>
   </si>
   <si>
     <t>TC_WEB_SESS_002</t>
